--- a/backups/Timesheet_2026-08-29.xlsx
+++ b/backups/Timesheet_2026-08-29.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2758" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2909" uniqueCount="702">
   <si>
     <t>Month</t>
   </si>
@@ -4134,7 +4134,7 @@
         <v>16.33</v>
       </c>
       <c r="F5" s="2">
-        <v>32.15</v>
+        <v>32.9</v>
       </c>
       <c r="G5" s="2">
         <v>19.25</v>
@@ -4146,7 +4146,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="2">
-        <v>170.48</v>
+        <v>171.23</v>
       </c>
       <c r="K5" s="2">
         <v>41</v>
@@ -12215,8 +12215,8 @@
       <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>15</v>
+      <c r="C30" s="3">
+        <v>0.75</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>15</v>
@@ -12233,11 +12233,11 @@
       <c r="H30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>15</v>
+      <c r="I30" s="3">
+        <v>0.75</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>15</v>
@@ -12729,7 +12729,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13619,6 +13619,499 @@
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
         <v>15</v>
       </c>
     </row>
